--- a/examples/lab-lipidomics/quant_input.xlsx
+++ b/examples/lab-lipidomics/quant_input.xlsx
@@ -191,7 +191,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Which class and adduct each polarity reports. Use TRUE or FALSE; a blank cell counts as TRUE. Ammonium acetate gives [M+CH3COO]- in negative mode, ammonium formate [M+HCOO]-.</t>
+          <t>Which class and adduct each polarity reports. Write TRUE or FALSE in every row's Use cell; a blank cell is a problem. Ammonium acetate gives [M+CH3COO]- in negative mode, ammonium formate [M+HCOO]-.</t>
         </is>
       </c>
     </row>
@@ -212,7 +212,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Numbers are written with a decimal point (0.5, not 0,5). Names, adducts and formulas are ASCII.</t>
+          <t>Numbers are written with a decimal point (0.5, not 0,5). Names, adducts and formulas are ASCII. A unit in a header's parentheses must agree with Settings (Spiked amount) or be minutes (RT).</t>
         </is>
       </c>
     </row>
@@ -301,10 +301,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4">
       <formula1>"uL plasma,mg tissue,10^6 cells"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B5">
       <formula1>"pmol,nmol,fmol"</formula1>
     </dataValidation>
   </dataValidations>
